--- a/tests/projectWorkSpace/Test/Test/TestData.xlsx
+++ b/tests/projectWorkSpace/Test/Test/TestData.xlsx
@@ -69,7 +69,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,6 +80,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -111,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -122,6 +128,9 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -136,6 +145,9 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -445,17 +457,17 @@
   <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="9" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="11" width="15.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -477,16 +489,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2"/>
@@ -510,97 +522,97 @@
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <v>912383278321</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="4">
         <v>321</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="4">
         <v>6</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="4">
         <v>2032</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="5"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="6"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="2"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="6"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="5"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="6"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="5"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="6"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="5"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="6"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="6"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
